--- a/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T08:26:42+00:00</t>
+    <t>2026-05-08T11:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T11:27:41+00:00</t>
+    <t>2026-05-11T05:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T05:47:08+00:00</t>
+    <t>2026-05-11T10:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/TMD-3109-ausbau-alte-authentisierung/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T10:53:43+00:00</t>
+    <t>2026-05-11T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
